--- a/456-préparation-publication-release-230/ig/StructureDefinition-tddui-patient-validation.xlsx
+++ b/456-préparation-publication-release-230/ig/StructureDefinition-tddui-patient-validation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T09:30:03+00:00</t>
+    <t>2026-03-16T09:41:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
